--- a/web/files/港岛-赤柱-Solace.xlsx
+++ b/web/files/港岛-赤柱-Solace.xlsx
@@ -806,7 +806,7 @@
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>2464</v>
+        <v>2496</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
         <v>96800000</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>39286</v>
+        <v>38782</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2362</v>
+        <v>2496</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1279,16 +1279,16 @@
       <c r="C6" s="17" t="inlineStr">
         <is>
           <t>52B号屋
-2464呎 (4+房)
+2496呎 (4+房)
 (26年-08月-14日)
 $9,680万
-$39,286/呎</t>
+$38,782/呎</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
           <t>52C号屋
-2362呎 (4+房)
+2496呎 (4+房)
 (在售)
 招标项目
 -</t>
